--- a/data/trans_orig/P20D2_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P20D2_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si durante su último ingreso estuvo acompañado/a por una mujer en 2023</t>
+          <t>Población según si durante su último ingreso estuvo acompañado/a por una mujer en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8064</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7182</t>
+          <t>6921</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>4719</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12206</t>
+          <t>12775</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>39,62%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2271</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9809</t>
+          <t>9466</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>331</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3408</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2860</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11460</t>
+          <t>11271</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>34,96%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6230</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13861</t>
+          <t>13840</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5287</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10451</t>
+          <t>10417</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13213</t>
+          <t>13173</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22662</t>
+          <t>22152</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>68,71%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11399</t>
+          <t>11642</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8993</t>
+          <t>8915</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19288</t>
+          <t>19295</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14040</t>
+          <t>14257</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>27630</t>
+          <t>27940</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,57%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>845</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7369</t>
+          <t>8055</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7458</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2894</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11452</t>
+          <t>11692</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>19,07%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18429</t>
+          <t>18634</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28589</t>
+          <t>28798</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5597</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16448</t>
+          <t>16467</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27305</t>
+          <t>27172</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42255</t>
+          <t>41853</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>68,26%</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4400</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4270</t>
+          <t>4338</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7292</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3555</t>
+          <t>3294</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11230</t>
+          <t>11358</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,73%</t>
         </is>
       </c>
     </row>
@@ -1755,97 +1755,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1554</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2266</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>6,09%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>14,51%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>29,47%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>468</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2378</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,09%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>2265</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>30,93%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2473</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>12,31%</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6312</t>
+          <t>6684</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>163</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2867</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6836</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14485</t>
+          <t>15197</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>82,59%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5485</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17288</t>
+          <t>17301</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19153</t>
+          <t>18608</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30958</t>
+          <t>31352</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27185</t>
+          <t>27379</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44790</t>
+          <t>45227</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,4%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>3991</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14848</t>
+          <t>14629</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>2851</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9286</t>
+          <t>9574</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8053</t>
+          <t>8040</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21233</t>
+          <t>20766</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36456</t>
+          <t>36577</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50242</t>
+          <t>50411</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13760</t>
+          <t>13734</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26012</t>
+          <t>26597</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>53182</t>
+          <t>53433</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>72689</t>
+          <t>73007</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>65,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P20D2_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P20D2_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3647</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7416</t>
+          <t>8313</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4338</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6921</t>
+          <t>7497</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7985</t>
+          <t>8485</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4719</t>
+          <t>4882</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12775</t>
+          <t>13890</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>40,13%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2271</t>
+          <t>2199</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9466</t>
+          <t>9992</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>543</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3262</t>
+          <t>4413</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6478</t>
+          <t>6960</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3196</t>
+          <t>3269</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11271</t>
+          <t>12494</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>36,1%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9913</t>
+          <t>10312</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>5992</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13840</t>
+          <t>14364</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7866</t>
+          <t>8854</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10417</t>
+          <t>11424</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>17779</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13173</t>
+          <t>13780</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22152</t>
+          <t>23601</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,19%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18745</t>
+          <t>19461</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18745</t>
+          <t>19461</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18745</t>
+          <t>19461</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>15150</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>15150</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>15150</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>32242</t>
+          <t>34611</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32242</t>
+          <t>34611</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32242</t>
+          <t>34611</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5503</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>2177</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11642</t>
+          <t>11534</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>14780</t>
+          <t>16176</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8915</t>
+          <t>9969</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19295</t>
+          <t>21279</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>20283</t>
+          <t>22239</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14257</t>
+          <t>15627</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>27940</t>
+          <t>30357</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>43,49%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>2939</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>843</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8055</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3597</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1465</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>7694</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>6542</t>
+          <t>6658</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11692</t>
+          <t>11908</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>24371</t>
+          <t>28550</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18634</t>
+          <t>22609</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28798</t>
+          <t>33477</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10114</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>7354</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16467</t>
+          <t>19314</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>34486</t>
+          <t>40900</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27172</t>
+          <t>32634</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41853</t>
+          <t>48235</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>69,11%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32819</t>
+          <t>37553</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32819</t>
+          <t>37553</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32819</t>
+          <t>37553</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28491</t>
+          <t>32245</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28491</t>
+          <t>32245</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28491</t>
+          <t>32245</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>61311</t>
+          <t>69798</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>61311</t>
+          <t>69798</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>61311</t>
+          <t>69798</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4028</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6236</t>
+          <t>7298</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4338</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>8868</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>7270</t>
+          <t>8372</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11358</t>
+          <t>12706</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,91%</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>472</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2266</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>472</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2560</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -1863,27 +1863,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9678</t>
+          <t>10113</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6684</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10712</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>1567</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>373</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>11679</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>7098</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15197</t>
+          <t>15752</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>76,75%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10712</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10712</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10712</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7689</t>
+          <t>9336</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7689</t>
+          <t>9336</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7689</t>
+          <t>9336</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>18401</t>
+          <t>20523</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>18401</t>
+          <t>20523</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>18401</t>
+          <t>20523</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10184</t>
+          <t>11077</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>5818</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17301</t>
+          <t>18504</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>25354</t>
+          <t>28019</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18608</t>
+          <t>20525</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31352</t>
+          <t>34264</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,22 +2163,22 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>35538</t>
+          <t>39096</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27379</t>
+          <t>30554</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45227</t>
+          <t>49187</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>39,37%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>3787</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>14553</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2851</t>
+          <t>2903</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9574</t>
+          <t>10079</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>13488</t>
+          <t>14091</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8040</t>
+          <t>8528</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20766</t>
+          <t>21911</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>17,54%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>43963</t>
+          <t>48976</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36577</t>
+          <t>41618</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50411</t>
+          <t>56405</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18966</t>
+          <t>22770</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13734</t>
+          <t>16904</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26597</t>
+          <t>30632</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>62928</t>
+          <t>71746</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>53433</t>
+          <t>61161</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>73007</t>
+          <t>81240</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,03%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>49677</t>
+          <t>56731</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49677</t>
+          <t>56731</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49677</t>
+          <t>56731</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>111954</t>
+          <t>124933</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>111954</t>
+          <t>124933</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>111954</t>
+          <t>124933</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
